--- a/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_DATA_SYSTEM_INTEGRATION.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_DATA_SYSTEM_INTEGRATION.xlsx
@@ -456,13 +456,13 @@
         <v>Application Programming Interface — Giao diện lập trình ứng dụng cho phép hai hệ thống phần mềm giao tiếp và trao đổi dữ liệu với nhau — cầu nối giao tiếp</v>
       </c>
       <c r="F2" t="str">
+        <v>Advanced Program Instruction — Tập lệnh nâng cao dùng để điều khiển card đồ họa máy tính — tập lệnh card màn hình</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Automated Product Index — Chỉ số sản phẩm tự động hiển thị trên website bán hàng thương mại điện tử — chỉ số sản phẩm</v>
+      </c>
+      <c r="H2" t="str">
         <v>Active Process Integration — Quy trình tích hợp các tiến trình đang chạy trên bộ nhớ RAM của máy chủ — quy trình bộ nhớ</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Advanced Program Instruction — Tập lệnh nâng cao dùng để điều khiển card đồ họa máy tính — tập lệnh card màn hình</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Automated Product Index — Chỉ số sản phẩm tự động hiển thị trên website bán hàng thương mại điện tử — chỉ số sản phẩm</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -482,19 +482,19 @@
         <v>JSON là định dạng dữ liệu dạng text nhẹ, sử dụng cặp key-value (tương tự như object của Javascript), là định dạng trao đổi dữ liệu phổ biến nhất hiện nay qua API.</v>
       </c>
       <c r="E3" t="str">
-        <v>Định dạng văn bản gọn nhẹ, dễ đọc viết đối với con người và dễ phân tích đối với máy tính dưới dạng key-value — định dạng key-value gọn nhẹ</v>
+        <v>Định dạng bảng tính Excel chứa các ô dữ liệu được ngăn cách bằng dấu phẩy — bảng tính CSV</v>
       </c>
       <c r="F3" t="str">
         <v>Định dạng mã hóa nhị phân phức tạp chỉ có bộ vi xử lý máy tính mới đọc hiểu được — mã hóa nhị phân</v>
       </c>
       <c r="G3" t="str">
-        <v>Định dạng bảng tính Excel chứa các ô dữ liệu được ngăn cách bằng dấu phẩy — bảng tính CSV</v>
+        <v>Ngôn ngữ đánh dấu siêu văn bản dùng để thiết kế màu sắc cho giao diện trang web — ngôn ngữ giao diện HTML</v>
       </c>
       <c r="H3" t="str">
-        <v>Ngôn ngữ đánh dấu siêu văn bản dùng để thiết kế màu sắc cho giao diện trang web — ngôn ngữ giao diện HTML</v>
+        <v>Định dạng văn bản gọn nhẹ, dễ đọc viết đối với con người và dễ phân tích đối với máy tính dưới dạng key-value — định dạng key-value gọn nhẹ</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>ERD là sơ đồ mối quan hệ thực thể, biểu diễn cấu trúc dữ liệu logic của hệ thống bằng các thực thể, thuộc tính và liên kết (1-1, 1-n, n-n) giữa chúng.</v>
       </c>
       <c r="E4" t="str">
-        <v>Các thực thể dữ liệu, các thuộc tính của chúng và mối quan hệ giữa các thực thể đó — sơ đồ mối quan hệ thực thể</v>
+        <v>Luồng đi của dữ liệu qua các tiến trình xử lý và nơi lưu trữ dữ liệu — sơ đồ luồng dữ liệu DFD</v>
       </c>
       <c r="F4" t="str">
-        <v>Luồng đi của dữ liệu qua các tiến trình xử lý và nơi lưu trữ dữ liệu — sơ đồ luồng dữ liệu DFD</v>
+        <v>Giao diện người dùng của các form đăng ký thông tin khách hàng — giao diện nhập liệu</v>
       </c>
       <c r="G4" t="str">
         <v>Thời gian phản hồi trung bình của cơ sở dữ liệu khi chạy truy vấn nặng — hiệu năng database</v>
       </c>
       <c r="H4" t="str">
-        <v>Giao diện người dùng của các form đăng ký thông tin khách hàng — giao diện nhập liệu</v>
+        <v>Các thực thể dữ liệu, các thuộc tính của chúng và mối quan hệ giữa các thực thể đó — sơ đồ mối quan hệ thực thể</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Theo chuẩn RESTful, POST dùng để gửi dữ liệu lên server để tạo mới tài nguyên (ví dụ: tạo mới đơn hàng, tài khoản).</v>
       </c>
       <c r="E5" t="str">
+        <v>GET — dùng để truy xuất và lấy dữ liệu từ máy chủ về hệ thống — lấy dữ liệu</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DELETE — dùng để xóa bỏ một tài nguyên đang lưu trữ trên máy chủ — xóa dữ liệu</v>
+      </c>
+      <c r="G5" t="str">
         <v>POST — dùng để tạo mới một tài nguyên hoặc gửi dữ liệu lên máy chủ — tạo mới tài nguyên</v>
-      </c>
-      <c r="F5" t="str">
-        <v>GET — dùng để truy xuất và lấy dữ liệu từ máy chủ về hệ thống — lấy dữ liệu</v>
-      </c>
-      <c r="G5" t="str">
-        <v>DELETE — dùng để xóa bỏ một tài nguyên đang lưu trữ trên máy chủ — xóa dữ liệu</v>
       </c>
       <c r="H5" t="str">
         <v>HEAD — dùng để kiểm tra thông tin tiêu đề header của API mà không lấy dữ liệu — kiểm tra header</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>XML sử dụng cấu trúc cây với các tag mở/đóng tự định nghĩa để lưu trữ dữ liệu. So với JSON, XML dài dòng và tốn băng thông truyền tải hơn.</v>
       </c>
       <c r="E6" t="str">
-        <v>Sử dụng các cặp thẻ lồng nhau (như &lt;the&gt;noi dung&lt;/the&gt;) để cấu trúc dữ liệu; có tính mô tả cao nhưng nặng hơn JSON — sử dụng thẻ lồng nhau</v>
+        <v>XML tự động mã hóa dữ liệu thành hình ảnh đồ họa 3D trước khi gửi đi — mã hóa hình ảnh</v>
       </c>
       <c r="F6" t="str">
         <v>XML chỉ lưu trữ được số nguyên còn JSON chỉ lưu trữ được chuỗi văn bản — giới hạn kiểu dữ liệu</v>
       </c>
       <c r="G6" t="str">
-        <v>XML tự động mã hóa dữ liệu thành hình ảnh đồ họa 3D trước khi gửi đi — mã hóa hình ảnh</v>
+        <v>Sử dụng các cặp thẻ lồng nhau (như &lt;the&gt;noi dung&lt;/the&gt;) để cấu trúc dữ liệu; có tính mô tả cao nhưng nặng hơn JSON — sử dụng thẻ lồng nhau</v>
       </c>
       <c r="H6" t="str">
         <v>XML bắt buộc phải chạy trên hệ điều hành Windows chứ không chạy được trên Linux — ràng buộc hệ điều hành</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Data Dictionary là tài liệu mô tả chi tiết siêu dữ liệu (metadata), định nghĩa rõ cấu trúc dữ liệu của các bảng (tên cột, kiểu dữ liệu: string/int, độ dài, khóa chính/khóa ngoại, mô tả ý nghĩa).</v>
       </c>
       <c r="E7" t="str">
+        <v>Liệt kê tất cả các tài khoản đăng nhập của người dùng trong hệ thống database — danh sách tài khoản</v>
+      </c>
+      <c r="F7" t="str">
         <v>Giải thích định nghĩa, kiểu dữ liệu, độ dài và ràng buộc của từng trường dữ liệu trong hệ thống — định nghĩa trường dữ liệu</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>Dịch các câu lệnh SQL từ tiếng Anh sang tiếng Việt cho khách hàng đọc hiểu — dịch thuật SQL</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Liệt kê tất cả các tài khoản đăng nhập của người dùng trong hệ thống database — danh sách tài khoản</v>
       </c>
       <c r="H7" t="str">
         <v>Từ điển giải thích các thuật ngữ tiếng Anh chuyên ngành của dự án — từ điển thuật ngữ</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Khóa ngoại (Foreign Key) là cột trong một bảng trỏ đến khóa chính (Primary Key) của bảng khác, dùng để thiết lập mối liên kết dữ liệu giữa các thực thể.</v>
       </c>
       <c r="E8" t="str">
+        <v>Dùng để đảm bảo giá trị trong cột đó là duy nhất và không được trùng lặp trong cùng một bảng — khóa duy nhất</v>
+      </c>
+      <c r="F8" t="str">
         <v>Dùng để liên kết một bảng này với bảng khác bằng cách trỏ tới khóa chính của bảng được liên kết — thiết lập quan hệ liên kết</v>
       </c>
-      <c r="F8" t="str">
-        <v>Dùng để đảm bảo giá trị trong cột đó là duy nhất và không được trùng lặp trong cùng một bảng — khóa duy nhất</v>
-      </c>
       <c r="G8" t="str">
+        <v>Dùng để mã hóa mật khẩu người dùng trước khi lưu trữ vào database — khóa mật khẩu</v>
+      </c>
+      <c r="H8" t="str">
         <v>Dùng để tự động tăng giá trị của trường số nguyên lên 1 đơn vị khi thêm hàng mới — tự động tăng</v>
       </c>
-      <c r="H8" t="str">
-        <v>Dùng để mã hóa mật khẩu người dùng trước khi lưu trữ vào database — khóa mật khẩu</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>Đầu số HTTP 2xx biểu thị sự thành công. Status Code 200 OK là mã phản hồi chuẩn cho thấy request đã được xử lý thành công.</v>
       </c>
       <c r="E9" t="str">
+        <v>Máy chủ gặp lỗi xử lý logic nội bộ và không thể trả về dữ liệu — lỗi máy chủ</v>
+      </c>
+      <c r="F9" t="str">
         <v>Yêu cầu đã được tiếp nhận và xử lý thành công từ phía máy chủ — thành công</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>Yêu cầu bị từ chối vì tài khoản của người dùng không có quyền truy cập — lỗi phân quyền</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Không tìm thấy địa chỉ URL của API trên máy chủ — không tìm thấy tài nguyên</v>
       </c>
-      <c r="H9" t="str">
-        <v>Máy chủ gặp lỗi xử lý logic nội bộ và không thể trả về dữ liệu — lỗi máy chủ</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Theo quy chuẩn REST API, PUT thay thế toàn bộ đối tượng bằng payload mới gửi lên (nếu thiếu trường sẽ bị set NULL hoặc default). PATCH cập nhật cục bộ chỉ những trường được gửi lên.</v>
       </c>
       <c r="E10" t="str">
+        <v>PUT chỉ dùng cho dữ liệu số; PATCH chỉ dùng cho dữ liệu chuỗi văn bản — giới hạn kiểu dữ liệu</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PUT gửi dữ liệu qua URL; PATCH gửi dữ liệu ẩn dưới thân Request Body — phương thức gửi nhận</v>
+      </c>
+      <c r="G10" t="str">
         <v>PUT dùng để cập nhật ghi đè toàn bộ tài nguyên; PATCH dùng để cập nhật một phần (chỉ các trường thay đổi) của tài nguyên — ghi đè vs cập nhật một phần</v>
-      </c>
-      <c r="F10" t="str">
-        <v>PUT chỉ dùng cho dữ liệu số; PATCH chỉ dùng cho dữ liệu chuỗi văn bản — giới hạn kiểu dữ liệu</v>
-      </c>
-      <c r="G10" t="str">
-        <v>PUT gửi dữ liệu qua URL; PATCH gửi dữ liệu ẩn dưới thân Request Body — phương thức gửi nhận</v>
       </c>
       <c r="H10" t="str">
         <v>PUT bắt buộc phải có chứng chỉ bảo mật SSL; PATCH có thể chạy qua giao thức HTTP thường — yêu cầu bảo mật</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Hệ quản trị CSDL quan hệ (RDBMS) không hỗ trợ trực tiếp quan hệ n-n ở tầng vật lý. BA/Designer phải phân rã quan hệ n-n thành hai quan hệ 1-n thông qua một bảng trung gian.</v>
       </c>
       <c r="E11" t="str">
+        <v>Không thể biểu diễn được quan hệ nhiều nhiều trong cơ sở dữ liệu quan hệ vật lý — giới hạn RDBMS</v>
+      </c>
+      <c r="F11" t="str">
         <v>Tạo ra một bảng trung gian (Junction/Association Table) chứa hai khóa ngoại trỏ tới khóa chính của hai bảng gốc — bảng trung gian liên kết</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>Vẽ một đường nối trực tiếp giữa hai bảng và ghi ký hiệu n-n ở hai đầu — ký hiệu sơ đồ</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Thêm trực tiếp một mảng (Array) các khóa ngoại vào trong một cột của bảng đối tác — lưu trữ dạng mảng</v>
       </c>
-      <c r="H11" t="str">
-        <v>Không thể biểu diễn được quan hệ nhiều nhiều trong cơ sở dữ liệu quan hệ vật lý — giới hạn RDBMS</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -772,19 +772,19 @@
         <v>Một API Spec hoàn chỉnh phải chứa đầy đủ thông tin kỹ thuật: URL nhận request, phương thức gọi, cấu trúc dữ liệu gửi đi (Request), dữ liệu nhận về khi thành công/thất bại (Response) để dev/test làm việc độc lập.</v>
       </c>
       <c r="E13" t="str">
+        <v>Màu sắc của nút bấm gọi API hiển thị trên màn hình ứng dụng di động — thiết kế nút bấm giao diện</v>
+      </c>
+      <c r="F13" t="str">
         <v>Endpoint URL, HTTP Method, Request Headers, Request Body Schema, Response Headers, Response Body Schema và Error Codes — đặc tả chi tiết API</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Số lượng dòng code cần viết để xử lý logic bên trong API đó — độ dài mã nguồn</v>
       </c>
       <c r="G13" t="str">
         <v>Tên và email của lập trình viên chịu trách nhiệm viết code cho API đó — nhân sự phát triển</v>
       </c>
       <c r="H13" t="str">
-        <v>Màu sắc của nút bấm gọi API hiển thị trên màn hình ứng dụng di động — thiết kế nút bấm giao diện</v>
+        <v>Số lượng dòng code cần viết để xử lý logic bên trong API đó — độ dài mã nguồn</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Chuẩn hóa dữ liệu (Normalization) giúp phân rã các bảng to thành bảng nhỏ logic hơn để tránh các bất thường khi thêm/sửa/xóa dữ liệu (Anomalies) và tiết kiệm không gian lưu trữ.</v>
       </c>
       <c r="E14" t="str">
+        <v>Tăng tốc độ hiển thị giao diện trang web lên dưới 1 giây — tối ưu giao diện</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Tự động sao lưu dữ liệu dự phòng từ máy chủ chính sang máy chủ phụ hàng ngày — sao lưu dữ liệu</v>
+      </c>
+      <c r="G14" t="str">
         <v>Giảm thiểu tối đa sự trùng lặp dữ liệu (Redundancy) và đảm bảo tính nhất quán của dữ liệu (Data Integrity) — tối ưu hóa cấu trúc</v>
       </c>
-      <c r="F14" t="str">
-        <v>Tăng tốc độ hiển thị giao diện trang web lên dưới 1 giây — tối ưu giao diện</v>
-      </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Mã hóa toàn bộ các bảng dữ liệu để hacker không thể đọc trộm thông tin — bảo mật dữ liệu</v>
       </c>
-      <c r="H14" t="str">
-        <v>Tự động sao lưu dữ liệu dự phòng từ máy chủ chính sang máy chủ phụ hàng ngày — sao lưu dữ liệu</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Mã 401 Unauthorized cho biết request cần được xác thực danh tính (Authentication). Tránh nhầm với 403 Forbidden (đã biết danh tính nhưng bị cấm truy cập).</v>
       </c>
       <c r="E15" t="str">
-        <v>Yêu cầu thiếu thông tin xác thực hợp lệ (như token hết hạn, sai username/password) — lỗi xác thực danh tính</v>
+        <v>Tham số gửi lên trong Request Body bị sai định dạng dữ liệu quy định — lỗi cú pháp request</v>
       </c>
       <c r="F15" t="str">
         <v>Tài khoản đã xác thực đúng nhưng không có quyền truy cập vào tài nguyên này — lỗi phân quyền truy cập</v>
       </c>
       <c r="G15" t="str">
-        <v>Tham số gửi lên trong Request Body bị sai định dạng dữ liệu quy định — lỗi cú pháp request</v>
+        <v>Yêu cầu thiếu thông tin xác thực hợp lệ (như token hết hạn, sai username/password) — lỗi xác thực danh tính</v>
       </c>
       <c r="H15" t="str">
         <v>Máy chủ cơ sở dữ liệu của hệ thống đang bị quá tải và không phản hồi — lỗi quá tải máy chủ</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Webhook là một API ngược. Thay vì hệ thống đích liên tục hỏi (polling) mất tài nguyên, hệ thống nguồn sẽ chủ động gọi API của hệ thống đích để thông báo khi có sự kiện mới (như có giao dịch mới).</v>
       </c>
       <c r="E16" t="str">
+        <v>Khi hệ thống đích phải liên tục gửi request sau mỗi 5 giây để kiểm tra xem hệ thống nguồn có gì mới không — cơ chế polling</v>
+      </c>
+      <c r="F16" t="str">
         <v>Khi hệ thống nguồn muốn tự động đẩy thông báo sự kiện (Event-driven) sang hệ thống đích ngay khi có dữ liệu mới phát sinh — đẩy dữ liệu chủ động</v>
       </c>
-      <c r="F16" t="str">
-        <v>Khi hệ thống đích phải liên tục gửi request sau mỗi 5 giây để kiểm tra xem hệ thống nguồn có gì mới không — cơ chế polling</v>
-      </c>
       <c r="G16" t="str">
+        <v>Khi cần thiết kế lại giao diện người dùng theo chuẩn responsive di động — responsive giao diện</v>
+      </c>
+      <c r="H16" t="str">
         <v>Khi cần mã hóa toàn bộ dữ liệu truyền tải qua đường truyền mạng internet — bảo mật đường truyền</v>
       </c>
-      <c r="H16" t="str">
-        <v>Khi cần thiết kế lại giao diện người dùng theo chuẩn responsive di động — responsive giao diện</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -891,13 +891,13 @@
         <v>Quy tắc chuyển đổi dữ liệu (Transformation Rules) để ánh xạ tương ứng: 0 thành "PENDING", 1 thành "PROCESSING", 2 thành "COMPLETED" — quy tắc chuyển đổi giá trị</v>
       </c>
       <c r="F17" t="str">
+        <v>Đề xuất xóa bỏ trường trạng thái đơn hàng để không cần thực hiện ánh xạ nữa — loại bỏ trường dữ liệu</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Yêu cầu khách hàng tự nhập tay chuyển đổi dữ liệu khi chạy hệ thống mới — chuyển đổi thủ công</v>
+      </c>
+      <c r="H17" t="str">
         <v>Yêu cầu hệ thống mới sửa lại code để lưu giá trị 0, 1, 2 giống hệt hệ thống cũ — sửa đổi hệ thống mới</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Đề xuất xóa bỏ trường trạng thái đơn hàng để không cần thực hiện ánh xạ nữa — loại bỏ trường dữ liệu</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Yêu cầu khách hàng tự nhập tay chuyển đổi dữ liệu khi chạy hệ thống mới — chuyển đổi thủ công</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -917,19 +917,19 @@
         <v>IPN là cơ chế gọi ngầm (Server-to-Server) giữa cổng thanh toán và máy chủ của bạn. Nếu khách hàng thanh toán xong mà tắt trình duyệt trước khi redirect về web, IPN vẫn đảm bảo server nhận được thông tin để cập nhật trạng thái đơn hàng thành "Đã thanh toán".</v>
       </c>
       <c r="E18" t="str">
+        <v>Để tự động trừ tiền trong tài khoản ngân hàng của khách hàng mà không cần mật khẩu OTP — trừ tiền tự động</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Để vẽ lại sơ đồ trang web bán hàng của đối tác theo tông màu thương hiệu của cổng thanh toán — đồng bộ giao diện</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Để tăng tốc độ tải trang thanh toán lên nhanh gấp đôi so với bình thường — tăng tốc tải trang</v>
+      </c>
+      <c r="H18" t="str">
         <v>Để đảm bảo hệ thống cập nhật đúng trạng thái đơn hàng của khách hàng ngay cả khi trình duyệt của khách hàng bị đóng hoặc mất kết nối đột ngột — cập nhật trạng thái tin cậy</v>
       </c>
-      <c r="F18" t="str">
-        <v>Để tự động trừ tiền trong tài khoản ngân hàng của khách hàng mà không cần mật khẩu OTP — trừ tiền tự động</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Để vẽ lại sơ đồ trang web bán hàng của đối tác theo tông màu thương hiệu của cổng thanh toán — đồng bộ giao diện</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Để tăng tốc độ tải trang thanh toán lên nhanh gấp đôi so với bình thường — tăng tốc tải trang</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1004,19 +1004,19 @@
         <v>Đây là bài toán kinh điển trong tích hợp dữ liệu. BA phải cung cấp quy tắc logic xử lý chuỗi rõ ràng (Transformation Rule), bao gồm cả cách xử lý các trường hợp đặc biệt (như tên nước ngoài, tên chỉ có 2 từ, hoặc tên có nhiều hơn 4 từ) để dev triển khai chính xác.</v>
       </c>
       <c r="E21" t="str">
-        <v>Đặc tả quy tắc xử lý chuỗi (String Manipulation): Khi truyền từ A sang B, viết thuật toán tách chuỗi `fullName` dựa trên khoảng trắng để phân bổ vào `firstName`, `lastName`, `middleName` và ngược lại khi truyền từ B sang A thì thực hiện ghép chuỗi kèm khoảng trắng — quy tắc tách ghép chuỗi nghiệp vụ</v>
+        <v>Chỉ ánh xạ trường `fullName` sang trường `firstName` của hệ thống B, bỏ trống hoàn toàn các trường `lastName` và `middleName` — chấp nhận mất mát dữ liệu</v>
       </c>
       <c r="F21" t="str">
         <v>Yêu cầu hệ thống B đập đi xây lại cấu trúc database để gộp 3 trường thành 1 trường `fullName` duy nhất cho giống hệ thống A — đập đi xây lại hệ thống</v>
       </c>
       <c r="G21" t="str">
-        <v>Chỉ ánh xạ trường `fullName` sang trường `firstName` của hệ thống B, bỏ trống hoàn toàn các trường `lastName` và `middleName` — chấp nhận mất mát dữ liệu</v>
+        <v>Đặc tả quy tắc xử lý chuỗi (String Manipulation): Khi truyền từ A sang B, viết thuật toán tách chuỗi `fullName` dựa trên khoảng trắng để phân bổ vào `firstName`, `lastName`, `middleName` và ngược lại khi truyền từ B sang A thì thực hiện ghép chuỗi kèm khoảng trắng — quy tắc tách ghép chuỗi nghiệp vụ</v>
       </c>
       <c r="H21" t="str">
         <v>Yêu cầu khách hàng tự thực hiện chuẩn hóa dữ liệu bằng tay trước khi hệ thống thực hiện truyền tải API — chuyển giao công việc</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1036,13 @@
         <v>Thiết kế đối soát 3 bước: Đối soát số lượng bản ghi (Record count), Đối soát tổng số tiền lũy kế (Hash totals/Financial totals) ở cả nguồn và đích, và Đối soát ngẫu nhiên chi tiết từng giao dịch của các tài khoản VIP — đối soát toàn vẹn đa tầng</v>
       </c>
       <c r="F22" t="str">
+        <v>Yêu cầu lập trình viên tự viết một đoạn mã tự động sửa số dư tài khoản của hệ thống mới cho khớp với số dư hệ thống cũ — sửa dữ liệu cưỡng bức</v>
+      </c>
+      <c r="G22" t="str">
         <v>Chỉ cần đếm xem tổng số dòng ở bảng nguồn có bằng tổng số dòng ở bảng đích sau khi chuyển đổi xong hay không — đối soát số lượng đơn giản</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Châm ngòi chạy thử hệ thống mới, nếu khách hàng nào gọi điện lên tổng đài báo mất tiền thì mới kiểm tra lại tài khoản đó — đối soát thụ động</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Yêu cầu lập trình viên tự viết một đoạn mã tự động sửa số dư tài khoản của hệ thống mới cho khớp với số dư hệ thống cũ — sửa dữ liệu cưỡng bức</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1062,19 +1062,19 @@
         <v>Trong tích hợp thanh toán, do lỗi mạng, hệ thống gửi request có thể gửi lại (retry). Nếu API không có tính Idempotency (bằng cách kiểm tra Idempotency Key duy nhất của giao dịch), hệ thống đích có thể xử lý trùng lặp, dẫn đến việc trừ tiền khách hàng 2 lần.</v>
       </c>
       <c r="E23" t="str">
+        <v>Để đảm bảo mật khẩu của khách hàng được thay đổi liên tục sau mỗi lần gọi API thanh toán thành công — bảo mật mật khẩu</v>
+      </c>
+      <c r="F23" t="str">
         <v>Để đảm bảo rằng nếu một API gọi thanh toán bị gửi trùng lặp nhiều lần (do mạng chập chờn, người dùng bấm nút nhiều lần), hệ thống chỉ thực hiện trừ tiền duy nhất một lần — ngăn chặn trừ tiền trùng lặp</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Để tự động tăng gấp đôi số tiền thanh toán nếu khách hàng thực hiện giao dịch vào giờ cao điểm của hệ thống — tăng doanh thu</v>
       </c>
       <c r="G23" t="str">
         <v>Để nén kích thước dữ liệu gửi đi qua mạng giúp API phản hồi nhanh hơn gấp 10 lần — tối ưu hóa tốc độ</v>
       </c>
       <c r="H23" t="str">
-        <v>Để đảm bảo mật khẩu của khách hàng được thay đổi liên tục sau mỗi lần gọi API thanh toán thành công — bảo mật mật khẩu</v>
+        <v>Để tự động tăng gấp đôi số tiền thanh toán nếu khách hàng thực hiện giao dịch vào giờ cao điểm của hệ thống — tăng doanh thu</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>SOAP là giao thức chuẩn hóa cao, bảo mật mạnh mẽ (WS-Security) và có file định nghĩa cấu trúc WSDL (Web Services Description Language) giúp validate dữ liệu chặt chẽ ở tầng XML. REST là phong cách kiến trúc nhẹ nhàng hơn, dùng JSON giúp giảm dung lượng mạng truyền tải, phù hợp cho Web/Mobile.</v>
       </c>
       <c r="E24" t="str">
+        <v>SOAP chỉ dành cho lập trình viên Java dùng; còn REST dành riêng cho lập trình viên Javascript — giới hạn công nghệ</v>
+      </c>
+      <c r="F24" t="str">
+        <v>SOAP không hỗ trợ bất kỳ phương thức bảo mật nào; còn REST bắt buộc sử dụng mã hóa HTTPS — so sánh bảo mật</v>
+      </c>
+      <c r="G24" t="str">
         <v>SOAP bắt buộc sử dụng định dạng XML và có tài liệu định nghĩa WSDL chặt chẽ; REST linh hoạt hỗ trợ nhiều định dạng (thường dùng JSON) và nhẹ hơn — SOAP XML WSDL vs REST JSON</v>
       </c>
-      <c r="F24" t="str">
+      <c r="H24" t="str">
         <v>SOAP chỉ chạy qua giao thức truyền file FTP; còn REST chạy qua giao thức HTTP thường — phương thức truyền tải</v>
       </c>
-      <c r="G24" t="str">
-        <v>SOAP không hỗ trợ bất kỳ phương thức bảo mật nào; còn REST bắt buộc sử dụng mã hóa HTTPS — so sánh bảo mật</v>
-      </c>
-      <c r="H24" t="str">
-        <v>SOAP chỉ dành cho lập trình viên Java dùng; còn REST dành riêng cho lập trình viên Javascript — giới hạn công nghệ</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Khi tích hợp với bên thứ ba có Rate Limiting, hệ thống của bạn phải kiểm soát tần suất gửi (Throttling). Sử dụng Message Queue (như RabbitMQ/ActiveMQ) giúp lưu trữ tạm thời yêu cầu và xử lý tuần tự (Rate-limiting consumer), đảm bảo không mất mát dữ liệu đơn hàng và không vi phạm chính sách của đối tác.</v>
       </c>
       <c r="E25" t="str">
+        <v>Yêu cầu lập trình viên viết code bỏ qua giới hạn Rate Limit của đối tác bằng cách sử dụng các tài khoản IP giả mạo — gian lận IP</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Gửi liên tục các request cho đến khi API của đối tác bị sập hoàn toàn và họ buộc phải mở khóa giới hạn — tấn công từ chối dịch vụ</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Khi hệ thống báo lỗi Rate Limit, tự động hiển thị thông báo lỗi lên màn hình và yêu cầu khách hàng tự quay lại mua hàng sau 1 tiếng — đẩy lỗi cho khách hàng</v>
+      </c>
+      <c r="H25" t="str">
         <v>Thiết kế hàng đợi tin nhắn (Message Queue) để lưu trữ các yêu cầu đẩy đơn sang đối tác, kết hợp cơ chế Worker chạy ngầm để lấy dần yêu cầu và gọi API đối tác với tần suất nằm trong giới hạn cho phép — hàng đợi kiểm soát Rate Limit</v>
       </c>
-      <c r="F25" t="str">
-        <v>Khi hệ thống báo lỗi Rate Limit, tự động hiển thị thông báo lỗi lên màn hình và yêu cầu khách hàng tự quay lại mua hàng sau 1 tiếng — đẩy lỗi cho khách hàng</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Gửi liên tục các request cho đến khi API của đối tác bị sập hoàn toàn và họ buộc phải mở khóa giới hạn — tấn công từ chối dịch vụ</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Yêu cầu lập trình viên viết code bỏ qua giới hạn Rate Limit của đối tác bằng cách sử dụng các tài khoản IP giả mạo — gian lận IP</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>SSO qua SAML 2.0 hoạt động dựa trên cơ chế tin cậy bằng chữ ký số. Người dùng không gửi mật khẩu cho SP. SP tin tưởng vào SAML Assertion (khẳng định xác thực) do IdP ký và gửi về qua trình duyệt. BA phải mô tả luồng đi của Assertion này để các bên cấu hình đúng hệ thống.</v>
       </c>
       <c r="E26" t="str">
+        <v>Đặc tả cách thức cơ sở dữ liệu của IdP tự động đồng bộ hóa mật khẩu dạng rõ (plaintext) sang cơ sở dữ liệu của SP — đồng bộ mật khẩu thô</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Đặc tả cách cài đặt phần mềm quản lý cookie của bên thứ ba lên trình duyệt của tất cả nhân viên — cài đặt phần mềm</v>
+      </c>
+      <c r="G26" t="str">
         <v>Đặc tả luồng điều hướng (Redirect) của trình duyệt người dùng, cách SP gửi AuthnRequest tới IdP, cách IdP xác thực người dùng và trả lại SAML Assertion chứa thông tin người dùng được ký số về cho SP — đặc tả luồng xác thực liên kết SAML</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Đặc tả cách thức cơ sở dữ liệu của IdP tự động đồng bộ hóa mật khẩu dạng rõ (plaintext) sang cơ sở dữ liệu của SP — đồng bộ mật khẩu thô</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Đặc tả cách cài đặt phần mềm quản lý cookie của bên thứ ba lên trình duyệt của tất cả nhân viên — cài đặt phần mềm</v>
       </c>
       <c r="H26" t="str">
         <v>Đặc tả luồng mã hóa ổ cứng của máy chủ lưu trữ dữ liệu người dùng ở cả hai công ty — mã hóa ổ cứng</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
